--- a/docs/audit-ergonomie-2026-10-16/grilles/rgaa-site-public.xlsx
+++ b/docs/audit-ergonomie-2026-10-16/grilles/rgaa-site-public.xlsx
@@ -536,15 +536,16 @@
           <t>Taux de conformité</t>
         </is>
       </c>
-      <c r="B9" s="3">
-        <f>IF(B8&gt;0,"non calculable : "&amp;B8&amp;" critère(s) non testé(s)",IF(B5+B6=0,"—",B5/(B5+B6)))</f>
-        <v/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>non calculé : échantillon non réglementaire, restitution au lecteur d’écran non testée (7.1, 7.5)</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Le taux (C / (C + NC)) ne se calcule que lorsque plus aucun critère n'est NT : complétez la grille.</t>
+          <t>Aucun taux n'est calculé : seuls les effectifs sont donnés. Ce n'est pas une déclaration d'accessibilité.</t>
         </is>
       </c>
     </row>
